--- a/data/administracion_de_tribunales/OP_Ley148_ex_parteEmitidas.xlsx
+++ b/data/administracion_de_tribunales/OP_Ley148_ex_parteEmitidas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\administracion_de_tribunales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7BDEBED-C125-4321-93AF-42D103A1CCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B78841F-C4DB-4878-ABE6-F63F0563EEE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7728" yWindow="2460" windowWidth="17280" windowHeight="9420" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020-2021" sheetId="3" r:id="rId1"/>
@@ -476,6 +476,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="2">
+        <f>SUM(C2:F2)</f>
         <v>11</v>
       </c>
       <c r="C2" s="2">
@@ -490,6 +491,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="2">
+        <f t="shared" ref="B3:B14" si="0">SUM(C3:F3)</f>
         <v>1</v>
       </c>
       <c r="D3" s="2">
@@ -501,7 +503,8 @@
         <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
       <c r="C4" s="2">
         <v>8</v>
@@ -521,7 +524,8 @@
         <v>9</v>
       </c>
       <c r="B5" s="2">
-        <v>24</v>
+        <f t="shared" si="0"/>
+        <v>36</v>
       </c>
       <c r="C5" s="2">
         <v>15</v>
@@ -541,7 +545,8 @@
         <v>10</v>
       </c>
       <c r="B6" s="2">
-        <v>20</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
       <c r="C6" s="2">
         <v>9</v>
@@ -558,7 +563,8 @@
         <v>11</v>
       </c>
       <c r="B7" s="2">
-        <v>22</v>
+        <f t="shared" si="0"/>
+        <v>34</v>
       </c>
       <c r="C7" s="2">
         <v>13</v>
@@ -578,7 +584,8 @@
         <v>12</v>
       </c>
       <c r="B8" s="2">
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="C8" s="2">
         <v>7</v>
@@ -598,6 +605,7 @@
         <v>13</v>
       </c>
       <c r="B9" s="2">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C9" s="2">
@@ -615,7 +623,8 @@
         <v>14</v>
       </c>
       <c r="B10" s="2">
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="C10" s="2">
         <v>2</v>
@@ -634,7 +643,10 @@
       <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="2"/>
+      <c r="B11" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -645,7 +657,8 @@
         <v>16</v>
       </c>
       <c r="B12" s="2">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="C12" s="2">
         <v>1</v>
@@ -661,8 +674,9 @@
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B13">
-        <v>11</v>
+      <c r="B13" s="2">
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="C13">
         <v>5</v>
@@ -681,8 +695,9 @@
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B14">
-        <v>5</v>
+      <c r="B14" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -700,7 +715,7 @@
       </c>
       <c r="B15" s="2">
         <f>SUM(B2:B14)</f>
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="C15" s="2">
         <f>SUM(C2:C14)</f>
@@ -762,7 +777,8 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>18</v>
+        <f>SUM(C2:F2)</f>
+        <v>17</v>
       </c>
       <c r="C2">
         <v>6</v>
@@ -782,7 +798,8 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <f t="shared" ref="B3:B14" si="0">SUM(C3:F3)</f>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -796,7 +813,8 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>24</v>
+        <f t="shared" si="0"/>
+        <v>44</v>
       </c>
       <c r="C4">
         <v>18</v>
@@ -816,7 +834,8 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>51</v>
+        <f t="shared" si="0"/>
+        <v>64</v>
       </c>
       <c r="C5">
         <v>17</v>
@@ -836,7 +855,8 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>23</v>
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>9</v>
@@ -853,7 +873,8 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>23</v>
+        <f t="shared" si="0"/>
+        <v>38</v>
       </c>
       <c r="C7">
         <v>14</v>
@@ -873,6 +894,7 @@
         <v>12</v>
       </c>
       <c r="B8">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C8">
@@ -887,7 +909,8 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -907,7 +930,8 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -918,7 +942,8 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -935,7 +960,8 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>23</v>
       </c>
       <c r="C12">
         <v>8</v>
@@ -955,7 +981,8 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>33</v>
+        <f t="shared" si="0"/>
+        <v>42</v>
       </c>
       <c r="C13">
         <v>21</v>
@@ -975,7 +1002,8 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -996,7 +1024,7 @@
       </c>
       <c r="B15">
         <f>SUM(B2:B14)</f>
-        <v>210</v>
+        <v>287</v>
       </c>
       <c r="C15">
         <f>SUM(C2:C14)</f>
@@ -1058,7 +1086,8 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <f>SUM(C2:F2)</f>
+        <v>5</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1072,7 +1101,8 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <f t="shared" ref="B3:B14" si="0">SUM(C3:F3)</f>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1089,7 +1119,8 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -1106,7 +1137,8 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>34</v>
+        <f t="shared" si="0"/>
+        <v>38</v>
       </c>
       <c r="C5">
         <v>12</v>
@@ -1126,7 +1158,8 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>13</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -1146,7 +1179,8 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>22</v>
+        <f t="shared" si="0"/>
+        <v>43</v>
       </c>
       <c r="C7">
         <v>10</v>
@@ -1166,7 +1200,8 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -1183,6 +1218,7 @@
         <v>13</v>
       </c>
       <c r="B9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D9">
@@ -1194,7 +1230,8 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1211,7 +1248,8 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -1228,7 +1266,8 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>17</v>
+        <f t="shared" si="0"/>
+        <v>21</v>
       </c>
       <c r="C12">
         <v>5</v>
@@ -1245,7 +1284,8 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>23</v>
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="C13">
         <v>8</v>
@@ -1262,7 +1302,8 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -1280,7 +1321,7 @@
       </c>
       <c r="B15">
         <f>SUM(B2:B14)</f>
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="C15">
         <f>SUM(C2:C14)</f>
@@ -1342,7 +1383,8 @@
         <v>6</v>
       </c>
       <c r="B2" s="3">
-        <v>11</v>
+        <f>SUM(C2:F2)</f>
+        <v>13</v>
       </c>
       <c r="C2" s="3">
         <v>6</v>
@@ -1362,7 +1404,8 @@
         <v>7</v>
       </c>
       <c r="B3" s="3">
-        <v>5</v>
+        <f t="shared" ref="B3:B14" si="0">SUM(C3:F3)</f>
+        <v>4</v>
       </c>
       <c r="C3" s="3">
         <v>3</v>
@@ -1378,7 +1421,8 @@
         <v>8</v>
       </c>
       <c r="B4" s="3">
-        <v>18</v>
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="C4" s="3">
         <v>2</v>
@@ -1398,7 +1442,8 @@
         <v>9</v>
       </c>
       <c r="B5" s="3">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>49</v>
       </c>
       <c r="C5" s="3">
         <v>11</v>
@@ -1418,7 +1463,8 @@
         <v>10</v>
       </c>
       <c r="B6" s="3">
-        <v>17</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3">
@@ -1436,7 +1482,8 @@
         <v>11</v>
       </c>
       <c r="B7" s="3">
-        <v>24</v>
+        <f t="shared" si="0"/>
+        <v>43</v>
       </c>
       <c r="C7" s="3">
         <v>12</v>
@@ -1454,7 +1501,8 @@
         <v>12</v>
       </c>
       <c r="B8" s="3">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="C8" s="3">
         <v>5</v>
@@ -1472,6 +1520,7 @@
         <v>13</v>
       </c>
       <c r="B9" s="3">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C9" s="3">
@@ -1490,7 +1539,8 @@
         <v>14</v>
       </c>
       <c r="B10" s="3">
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
       <c r="C10" s="3">
         <v>5</v>
@@ -1508,7 +1558,8 @@
         <v>15</v>
       </c>
       <c r="B11" s="3">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
@@ -1526,7 +1577,8 @@
         <v>16</v>
       </c>
       <c r="B12" s="3">
-        <v>29</v>
+        <f t="shared" si="0"/>
+        <v>36</v>
       </c>
       <c r="C12" s="3">
         <v>10</v>
@@ -1546,7 +1598,8 @@
         <v>17</v>
       </c>
       <c r="B13" s="3">
-        <v>29</v>
+        <f t="shared" si="0"/>
+        <v>23</v>
       </c>
       <c r="C13" s="3">
         <v>10</v>
@@ -1566,6 +1619,7 @@
         <v>18</v>
       </c>
       <c r="B14" s="3">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C14" s="3">
@@ -1586,7 +1640,8 @@
         <v>19</v>
       </c>
       <c r="B15" s="3">
-        <v>222</v>
+        <f>SUM(B2:B14)</f>
+        <v>247</v>
       </c>
       <c r="C15" s="3">
         <v>71</v>
@@ -1637,19 +1692,20 @@
         <v>6</v>
       </c>
       <c r="B2" s="3">
-        <v>16</v>
+        <f>SUM(C2:F2)</f>
+        <v>23</v>
       </c>
       <c r="C2" s="3">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3">
         <v>7</v>
-      </c>
-      <c r="D2" s="3">
-        <v>2</v>
       </c>
       <c r="E2" s="3">
         <v>7</v>
       </c>
       <c r="F2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1657,10 +1713,11 @@
         <v>7</v>
       </c>
       <c r="B3" s="3">
-        <v>7</v>
+        <f t="shared" ref="B3:B14" si="0">SUM(C3:F3)</f>
+        <v>11</v>
       </c>
       <c r="C3" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3">
         <v>3</v>
@@ -1677,16 +1734,17 @@
         <v>8</v>
       </c>
       <c r="B4" s="3">
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="C4" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="3">
+        <v>6</v>
+      </c>
+      <c r="E4" s="3">
         <v>7</v>
-      </c>
-      <c r="E4" s="3">
-        <v>11</v>
       </c>
       <c r="F4" s="3">
         <v>3</v>
@@ -1697,19 +1755,20 @@
         <v>9</v>
       </c>
       <c r="B5" s="3">
-        <v>53</v>
+        <f t="shared" si="0"/>
+        <v>68</v>
       </c>
       <c r="C5" s="3">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D5" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E5" s="3">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1717,19 +1776,20 @@
         <v>10</v>
       </c>
       <c r="B6" s="3">
-        <v>34</v>
+        <f t="shared" si="0"/>
+        <v>54</v>
       </c>
       <c r="C6" s="3">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D6" s="3">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E6" s="3">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1737,19 +1797,20 @@
         <v>11</v>
       </c>
       <c r="B7" s="3">
-        <v>23</v>
+        <f t="shared" si="0"/>
+        <v>49</v>
       </c>
       <c r="C7" s="3">
+        <v>12</v>
+      </c>
+      <c r="D7" s="3">
         <v>14</v>
       </c>
-      <c r="D7" s="3">
-        <v>18</v>
-      </c>
       <c r="E7" s="3">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1757,19 +1818,20 @@
         <v>12</v>
       </c>
       <c r="B8" s="3">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="C8" s="3">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D8" s="3">
         <v>0</v>
       </c>
       <c r="E8" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1777,16 +1839,17 @@
         <v>13</v>
       </c>
       <c r="B9" s="3">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="C9" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" s="3">
         <v>3</v>
       </c>
       <c r="E9" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
@@ -1797,19 +1860,20 @@
         <v>14</v>
       </c>
       <c r="B10" s="3">
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>21</v>
       </c>
       <c r="C10" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1817,13 +1881,14 @@
         <v>15</v>
       </c>
       <c r="B11" s="3">
-        <v>16</v>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="C11" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D11" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E11" s="3">
         <v>5</v>
@@ -1837,19 +1902,20 @@
         <v>16</v>
       </c>
       <c r="B12" s="3">
-        <v>37</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="C12" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D12" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E12" s="3">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F12" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -1857,16 +1923,17 @@
         <v>17</v>
       </c>
       <c r="B13" s="3">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="C13" s="3">
+        <v>15</v>
+      </c>
+      <c r="D13" s="3">
         <v>24</v>
       </c>
-      <c r="C13" s="3">
-        <v>10</v>
-      </c>
-      <c r="D13" s="3">
-        <v>7</v>
-      </c>
       <c r="E13" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F13" s="3">
         <v>1</v>
@@ -1877,16 +1944,17 @@
         <v>18</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="C14" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D14" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E14" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1898,22 +1966,22 @@
       </c>
       <c r="B15" s="3">
         <f>SUM(B2:B14)</f>
-        <v>264</v>
+        <v>360</v>
       </c>
       <c r="C15" s="3">
-        <f t="shared" ref="C15:F15" si="0">SUM(C2:C14)</f>
-        <v>109</v>
+        <f t="shared" ref="C15:F15" si="1">SUM(C2:C14)</f>
+        <v>122</v>
       </c>
       <c r="D15" s="3">
-        <f t="shared" si="0"/>
-        <v>70</v>
+        <f t="shared" si="1"/>
+        <v>98</v>
       </c>
       <c r="E15" s="3">
-        <f t="shared" si="0"/>
-        <v>95</v>
+        <f t="shared" si="1"/>
+        <v>127</v>
       </c>
       <c r="F15" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
     </row>
